--- a/Config/Client_Config.xlsx
+++ b/Config/Client_Config.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
   <si>
     <t>Branch Name</t>
   </si>
@@ -106,6 +106,21 @@
   </si>
   <si>
     <t>1lhq_zUW-vbdE65NSbxkQdkWFdmznVNk5</t>
+  </si>
+  <si>
+    <t>Kattuppakkom</t>
+  </si>
+  <si>
+    <t>ANUK_1001860</t>
+  </si>
+  <si>
+    <t>TMCV-Ser-S-TN1-1001860-Kattupakka-DSvCM</t>
+  </si>
+  <si>
+    <t>Madhavaram</t>
+  </si>
+  <si>
+    <t>TMCV-Ser-S-CHN-1001860-Madhavaram-DSvCM</t>
   </si>
 </sst>
 </file>
@@ -207,13 +222,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -226,6 +237,15 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -583,7 +603,7 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -591,43 +611,65 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="15">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="7" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="2"/>
+      <c r="A3" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="4" spans="1:5" ht="15">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="2"/>
+      <c r="A4" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E2"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
+    <hyperlink ref="E3" r:id="rId2"/>
+    <hyperlink ref="E4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>
 
@@ -641,10 +683,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="3" t="s">
         <v>9</v>
       </c>
     </row>
@@ -660,7 +702,7 @@
       <c r="A3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="4" t="s">
         <v>12</v>
       </c>
     </row>

--- a/Config/Client_Config.xlsx
+++ b/Config/Client_Config.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
   <si>
     <t>Branch Name</t>
   </si>
@@ -81,27 +81,15 @@
     <t>SenderEmail</t>
   </si>
   <si>
-    <t>testquadan@gmail.com</t>
-  </si>
-  <si>
     <t>EmailPassword</t>
   </si>
   <si>
-    <t>ldpa zvpf wqkm tukc</t>
-  </si>
-  <si>
     <t>StatusFolderId  </t>
   </si>
   <si>
     <t>RootFolderId</t>
   </si>
   <si>
-    <t>StatusFileName</t>
-  </si>
-  <si>
-    <t>StatusTracker.xlsx</t>
-  </si>
-  <si>
     <t>1nBXAMP28x_bG5B_yFbg2vK_9D2ckjaKT</t>
   </si>
   <si>
@@ -121,6 +109,12 @@
   </si>
   <si>
     <t>TMCV-Ser-S-CHN-1001860-Madhavaram-DSvCM</t>
+  </si>
+  <si>
+    <t>cor.rpa.srvclaims@pmmil.com</t>
+  </si>
+  <si>
+    <t>udzn ybdc jaif akvx</t>
   </si>
 </sst>
 </file>
@@ -629,16 +623,16 @@
     </row>
     <row r="3" spans="1:5" ht="15">
       <c r="A3" s="11" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C3" s="10" t="s">
         <v>6</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E3" s="13" t="s">
         <v>5</v>
@@ -646,16 +640,16 @@
     </row>
     <row r="4" spans="1:5" ht="15">
       <c r="A4" s="11" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>6</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E4" s="13" t="s">
         <v>5</v>
@@ -675,7 +669,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="19.125" customWidth="1"/>
@@ -710,49 +704,64 @@
       <c r="A4" t="s">
         <v>16</v>
       </c>
-      <c r="B4" t="s">
-        <v>17</v>
+      <c r="B4" s="4" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B4" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="399697c3-5931-482a-bf60-528e1410a718" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="69774094-9380-4fae-b934-13dda1a7dd00">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010044376E494BD8C84F84CDAE7F49671CB7" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="976d064ff5353b1784c9cc50294987ed">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="69774094-9380-4fae-b934-13dda1a7dd00" xmlns:ns3="399697c3-5931-482a-bf60-528e1410a718" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6d25ac32989da96868f130ee3b29a1a8" ns2:_="" ns3:_="">
     <xsd:import namespace="69774094-9380-4fae-b934-13dda1a7dd00"/>
@@ -1007,27 +1016,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EADD28A-BF2C-45E6-83DF-53D59D707908}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="399697c3-5931-482a-bf60-528e1410a718"/>
+    <ds:schemaRef ds:uri="69774094-9380-4fae-b934-13dda1a7dd00"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="399697c3-5931-482a-bf60-528e1410a718" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="69774094-9380-4fae-b934-13dda1a7dd00">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{065CC945-652E-4DFC-A1A9-9FF2FC932111}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1860C180-34A5-4519-8E01-EE45D69AD4EA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1044,23 +1052,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{065CC945-652E-4DFC-A1A9-9FF2FC932111}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EADD28A-BF2C-45E6-83DF-53D59D707908}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="399697c3-5931-482a-bf60-528e1410a718"/>
-    <ds:schemaRef ds:uri="69774094-9380-4fae-b934-13dda1a7dd00"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Config/Client_Config.xlsx
+++ b/Config/Client_Config.xlsx
@@ -9,14 +9,14 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="5" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$3</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
   <si>
     <t>Branch Name</t>
   </si>
@@ -96,25 +96,22 @@
     <t>1lhq_zUW-vbdE65NSbxkQdkWFdmznVNk5</t>
   </si>
   <si>
-    <t>Kattuppakkom</t>
-  </si>
-  <si>
-    <t>ANUK_1001860</t>
-  </si>
-  <si>
-    <t>TMCV-Ser-S-TN1-1001860-Kattupakka-DSvCM</t>
-  </si>
-  <si>
-    <t>Madhavaram</t>
-  </si>
-  <si>
-    <t>TMCV-Ser-S-CHN-1001860-Madhavaram-DSvCM</t>
-  </si>
-  <si>
     <t>cor.rpa.srvclaims@pmmil.com</t>
   </si>
   <si>
     <t>udzn ybdc jaif akvx</t>
+  </si>
+  <si>
+    <t>Hosur</t>
+  </si>
+  <si>
+    <t>W._100A080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apr10@2025  </t>
+  </si>
+  <si>
+    <t>TMCV-Ser-S-TN-100A080-Hosur-DSvCM</t>
   </si>
 </sst>
 </file>
@@ -216,7 +213,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -240,6 +237,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -577,7 +577,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14.125" bestFit="1" customWidth="1"/>
@@ -604,63 +604,46 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15">
-      <c r="A2" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="7" t="s">
+    <row r="2" spans="1:5" s="10" customFormat="1" ht="15">
+      <c r="A2" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="13" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15">
-      <c r="A3" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" s="10" t="s">
+      <c r="A3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="15">
-      <c r="A4" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="13" t="s">
+      <c r="D3" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E2"/>
+  <autoFilter ref="A1:E3"/>
   <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1"/>
-    <hyperlink ref="E3" r:id="rId2"/>
-    <hyperlink ref="E4" r:id="rId3"/>
+    <hyperlink ref="E3" r:id="rId1"/>
+    <hyperlink ref="E2" r:id="rId2"/>
+    <hyperlink ref="C2" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId4"/>
@@ -705,7 +688,7 @@
         <v>16</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -713,7 +696,7 @@
         <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -742,26 +725,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="399697c3-5931-482a-bf60-528e1410a718" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="69774094-9380-4fae-b934-13dda1a7dd00">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010044376E494BD8C84F84CDAE7F49671CB7" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="976d064ff5353b1784c9cc50294987ed">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="69774094-9380-4fae-b934-13dda1a7dd00" xmlns:ns3="399697c3-5931-482a-bf60-528e1410a718" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6d25ac32989da96868f130ee3b29a1a8" ns2:_="" ns3:_="">
     <xsd:import namespace="69774094-9380-4fae-b934-13dda1a7dd00"/>
@@ -1016,26 +979,27 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="399697c3-5931-482a-bf60-528e1410a718" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="69774094-9380-4fae-b934-13dda1a7dd00">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EADD28A-BF2C-45E6-83DF-53D59D707908}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="399697c3-5931-482a-bf60-528e1410a718"/>
-    <ds:schemaRef ds:uri="69774094-9380-4fae-b934-13dda1a7dd00"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{065CC945-652E-4DFC-A1A9-9FF2FC932111}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1860C180-34A5-4519-8E01-EE45D69AD4EA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1052,4 +1016,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{065CC945-652E-4DFC-A1A9-9FF2FC932111}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EADD28A-BF2C-45E6-83DF-53D59D707908}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="399697c3-5931-482a-bf60-528e1410a718"/>
+    <ds:schemaRef ds:uri="69774094-9380-4fae-b934-13dda1a7dd00"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Config/Client_Config.xlsx
+++ b/Config/Client_Config.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Sheet2" sheetId="5" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$4</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
   <si>
     <t>Branch Name</t>
   </si>
@@ -48,77 +48,83 @@
     <t>benly.polly@quadance.com</t>
   </si>
   <si>
+    <t>Digital Signature Name</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Anu Krishna</t>
+  </si>
+  <si>
+    <t>Digital Signature Pin</t>
+  </si>
+  <si>
+    <t>ABCD@1234</t>
+  </si>
+  <si>
+    <t>SenderEmail</t>
+  </si>
+  <si>
+    <t>EmailPassword</t>
+  </si>
+  <si>
+    <t>StatusFolderId  </t>
+  </si>
+  <si>
+    <t>RootFolderId</t>
+  </si>
+  <si>
+    <t>1nBXAMP28x_bG5B_yFbg2vK_9D2ckjaKT</t>
+  </si>
+  <si>
+    <t>1lhq_zUW-vbdE65NSbxkQdkWFdmznVNk5</t>
+  </si>
+  <si>
+    <t>cor.rpa.srvclaims@pmmil.com</t>
+  </si>
+  <si>
+    <t>udzn ybdc jaif akvx</t>
+  </si>
+  <si>
+    <t>Hosur</t>
+  </si>
+  <si>
+    <t>W._100A080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apr10@2025  </t>
+  </si>
+  <si>
+    <t>TMCV-Ser-S-TN-100A080-Hosur-DSvCM</t>
+  </si>
+  <si>
+    <t>Chengalpet</t>
+  </si>
+  <si>
+    <t>ANUK_1001860</t>
+  </si>
+  <si>
     <t>Master#9846</t>
   </si>
   <si>
-    <t>Digital Signature Name</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Anu Krishna</t>
-  </si>
-  <si>
-    <t>Digital Signature Pin</t>
-  </si>
-  <si>
-    <t>ABCD@1234</t>
-  </si>
-  <si>
-    <t>Ekm Ser 3</t>
-  </si>
-  <si>
-    <t>ANUK_2082996</t>
-  </si>
-  <si>
-    <t>TMCV-Ser-S-KL2-2082996-Cochin-DSvCM</t>
-  </si>
-  <si>
-    <t>SenderEmail</t>
-  </si>
-  <si>
-    <t>EmailPassword</t>
-  </si>
-  <si>
-    <t>StatusFolderId  </t>
-  </si>
-  <si>
-    <t>RootFolderId</t>
-  </si>
-  <si>
-    <t>1nBXAMP28x_bG5B_yFbg2vK_9D2ckjaKT</t>
-  </si>
-  <si>
-    <t>1lhq_zUW-vbdE65NSbxkQdkWFdmznVNk5</t>
-  </si>
-  <si>
-    <t>cor.rpa.srvclaims@pmmil.com</t>
-  </si>
-  <si>
-    <t>udzn ybdc jaif akvx</t>
-  </si>
-  <si>
-    <t>Hosur</t>
-  </si>
-  <si>
-    <t>W._100A080</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apr10@2025  </t>
-  </si>
-  <si>
-    <t>TMCV-Ser-S-TN-100A080-Hosur-DSvCM</t>
+    <t>TMCV-Ser-S-CHN-1001860-Chenglpatu-DSvCM</t>
+  </si>
+  <si>
+    <t>Kattuppakkom</t>
+  </si>
+  <si>
+    <t>TMCV-Ser-S-TN1-1001860-Kattupakka-DSvCM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -164,12 +170,6 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -213,7 +213,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -221,15 +221,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -242,6 +233,14 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -577,7 +576,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14.125" bestFit="1" customWidth="1"/>
@@ -604,49 +603,67 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="10" customFormat="1" ht="15">
-      <c r="A2" s="11" t="s">
+    <row r="2" spans="1:5" s="11" customFormat="1" ht="15">
+      <c r="A2" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="14" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15">
-      <c r="A3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="7" t="s">
+    <row r="3" spans="1:5" s="5" customFormat="1" ht="15">
+      <c r="A3" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" s="5" customFormat="1" ht="15">
+      <c r="A4" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="8" t="s">
         <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E3"/>
+  <autoFilter ref="A1:E4"/>
   <hyperlinks>
-    <hyperlink ref="E3" r:id="rId1"/>
-    <hyperlink ref="E2" r:id="rId2"/>
-    <hyperlink ref="C2" r:id="rId3"/>
+    <hyperlink ref="E4" r:id="rId1"/>
+    <hyperlink ref="C4" r:id="rId2"/>
+    <hyperlink ref="E2" r:id="rId3"/>
+    <hyperlink ref="E3" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId4"/>
+  <pageSetup orientation="portrait" r:id="rId5"/>
 </worksheet>
 </file>
 
@@ -661,58 +678,58 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15">
       <c r="A1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>11</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Client_Config.xlsx
+++ b/Config/Client_Config.xlsx
@@ -12,11 +12,11 @@
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="5" r:id="rId2"/>
+    <sheet name="Login_Credentials" sheetId="4" r:id="rId1"/>
+    <sheet name="Other_Credentials" sheetId="5" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Login_Credentials!$A$1:$E$4</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="34">
   <si>
     <t>Branch Name</t>
   </si>
@@ -118,6 +118,18 @@
   </si>
   <si>
     <t>TMCV-Ser-S-TN1-1001860-Kattupakka-DSvCM</t>
+  </si>
+  <si>
+    <t>RecipientTo</t>
+  </si>
+  <si>
+    <t>vishnu.s@quadance.com;benly.polly@quadance.com</t>
+  </si>
+  <si>
+    <t>RecipientCc</t>
+  </si>
+  <si>
+    <t>vishnu.s@quadance.com</t>
   </si>
 </sst>
 </file>
@@ -669,11 +681,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="19.125" customWidth="1"/>
-    <col min="2" max="2" width="36.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15">
@@ -732,16 +744,54 @@
         <v>16</v>
       </c>
     </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B4" r:id="rId1"/>
+    <hyperlink ref="B8" r:id="rId2"/>
+    <hyperlink ref="B9" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="399697c3-5931-482a-bf60-528e1410a718" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="69774094-9380-4fae-b934-13dda1a7dd00">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010044376E494BD8C84F84CDAE7F49671CB7" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="976d064ff5353b1784c9cc50294987ed">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="69774094-9380-4fae-b934-13dda1a7dd00" xmlns:ns3="399697c3-5931-482a-bf60-528e1410a718" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6d25ac32989da96868f130ee3b29a1a8" ns2:_="" ns3:_="">
     <xsd:import namespace="69774094-9380-4fae-b934-13dda1a7dd00"/>
@@ -996,27 +1046,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{065CC945-652E-4DFC-A1A9-9FF2FC932111}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="399697c3-5931-482a-bf60-528e1410a718" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="69774094-9380-4fae-b934-13dda1a7dd00">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EADD28A-BF2C-45E6-83DF-53D59D707908}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="399697c3-5931-482a-bf60-528e1410a718"/>
+    <ds:schemaRef ds:uri="69774094-9380-4fae-b934-13dda1a7dd00"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1860C180-34A5-4519-8E01-EE45D69AD4EA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1033,23 +1082,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{065CC945-652E-4DFC-A1A9-9FF2FC932111}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EADD28A-BF2C-45E6-83DF-53D59D707908}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="399697c3-5931-482a-bf60-528e1410a718"/>
-    <ds:schemaRef ds:uri="69774094-9380-4fae-b934-13dda1a7dd00"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Config/Client_Config.xlsx
+++ b/Config/Client_Config.xlsx
@@ -9,14 +9,14 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Login_Credentials" sheetId="4" r:id="rId1"/>
-    <sheet name="Other_Credentials" sheetId="5" r:id="rId2"/>
+    <sheet name="NextGenCredentials" sheetId="4" r:id="rId1"/>
+    <sheet name="Assets" sheetId="5" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Login_Credentials!$A$1:$E$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">NextGenCredentials!$A$1:$E$4</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="35">
   <si>
     <t>Branch Name</t>
   </si>
@@ -130,6 +130,9 @@
   </si>
   <si>
     <t>vishnu.s@quadance.com</t>
+  </si>
+  <si>
+    <t>Descriptions</t>
   </si>
 </sst>
 </file>
@@ -681,22 +684,26 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="19.125" customWidth="1"/>
     <col min="2" max="2" width="45.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15">
+    <row r="1" spans="1:3" ht="15">
       <c r="A1" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
+      <c r="C1" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -704,7 +711,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -712,7 +719,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -720,7 +727,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -728,7 +735,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -736,7 +743,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -744,7 +751,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:3">
       <c r="A8" s="12" t="s">
         <v>30</v>
       </c>
@@ -752,7 +759,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:3">
       <c r="A9" s="12" t="s">
         <v>32</v>
       </c>
@@ -781,17 +788,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="399697c3-5931-482a-bf60-528e1410a718" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="69774094-9380-4fae-b934-13dda1a7dd00">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010044376E494BD8C84F84CDAE7F49671CB7" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="976d064ff5353b1784c9cc50294987ed">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="69774094-9380-4fae-b934-13dda1a7dd00" xmlns:ns3="399697c3-5931-482a-bf60-528e1410a718" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6d25ac32989da96868f130ee3b29a1a8" ns2:_="" ns3:_="">
     <xsd:import namespace="69774094-9380-4fae-b934-13dda1a7dd00"/>
@@ -1046,6 +1042,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="399697c3-5931-482a-bf60-528e1410a718" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="69774094-9380-4fae-b934-13dda1a7dd00">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{065CC945-652E-4DFC-A1A9-9FF2FC932111}">
   <ds:schemaRefs>
@@ -1055,17 +1062,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EADD28A-BF2C-45E6-83DF-53D59D707908}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="399697c3-5931-482a-bf60-528e1410a718"/>
-    <ds:schemaRef ds:uri="69774094-9380-4fae-b934-13dda1a7dd00"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1860C180-34A5-4519-8E01-EE45D69AD4EA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1082,4 +1078,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EADD28A-BF2C-45E6-83DF-53D59D707908}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="399697c3-5931-482a-bf60-528e1410a718"/>
+    <ds:schemaRef ds:uri="69774094-9380-4fae-b934-13dda1a7dd00"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Config/Client_Config.xlsx
+++ b/Config/Client_Config.xlsx
@@ -779,12 +779,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="399697c3-5931-482a-bf60-528e1410a718" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="69774094-9380-4fae-b934-13dda1a7dd00">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1043,20 +1045,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="399697c3-5931-482a-bf60-528e1410a718" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="69774094-9380-4fae-b934-13dda1a7dd00">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{065CC945-652E-4DFC-A1A9-9FF2FC932111}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EADD28A-BF2C-45E6-83DF-53D59D707908}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="399697c3-5931-482a-bf60-528e1410a718"/>
+    <ds:schemaRef ds:uri="69774094-9380-4fae-b934-13dda1a7dd00"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1081,12 +1084,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EADD28A-BF2C-45E6-83DF-53D59D707908}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{065CC945-652E-4DFC-A1A9-9FF2FC932111}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="399697c3-5931-482a-bf60-528e1410a718"/>
-    <ds:schemaRef ds:uri="69774094-9380-4fae-b934-13dda1a7dd00"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Config/Client_Config.xlsx
+++ b/Config/Client_Config.xlsx
@@ -7,7 +7,7 @@
     <sheet state="visible" name="Assets" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">NextGenCredentials!$A$1:$E$4</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">NextGenCredentials!$A$1:$E$6</definedName>
   </definedNames>
   <calcPr/>
   <extLst>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="52">
   <si>
     <t>Branch Name</t>
   </si>
@@ -67,6 +67,57 @@
   </si>
   <si>
     <t>TMCV-Ser-S-TN-100A080-Hosur-DSvCM</t>
+  </si>
+  <si>
+    <t>Kollam Ser 2</t>
+  </si>
+  <si>
+    <t>AK20_1006050</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="&quot;Aptos Narrow&quot;, sans-serif"/>
+        <color rgb="FF1155CC"/>
+        <sz val="11.0"/>
+        <u/>
+      </rPr>
+      <t>March@2025#</t>
+    </r>
+  </si>
+  <si>
+    <t>TMCV-Ser-S-KL2-1006050-Kollamscv-DSvCM</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="&quot;Aptos Narrow&quot;, sans-serif"/>
+        <color rgb="FF1155CC"/>
+        <sz val="11.0"/>
+        <u/>
+      </rPr>
+      <t>benly.polly@quadance.com</t>
+    </r>
+  </si>
+  <si>
+    <t>Ekm Ser 3</t>
+  </si>
+  <si>
+    <t>ANUK_2082996</t>
+  </si>
+  <si>
+    <t>TMCV-Ser-S-KL2-2082996-Cochin-DSvCM</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="&quot;Aptos Narrow&quot;, sans-serif"/>
+        <color rgb="FF1155CC"/>
+        <sz val="11.0"/>
+        <u/>
+      </rPr>
+      <t>benly.polly@quadance.com</t>
+    </r>
   </si>
   <si>
     <t>Name</t>
@@ -154,7 +205,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="13">
+  <fonts count="17">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -200,6 +251,28 @@
       <name val="Aptos Narrow"/>
     </font>
     <font>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="&quot;Aptos Narrow&quot;"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11.0"/>
+      <color rgb="FF0000FF"/>
+      <name val="&quot;Aptos Narrow&quot;"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11.0"/>
+      <color rgb="FF0000FF"/>
+      <name val="&quot;Aptos Narrow&quot;"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <b/>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -241,7 +314,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border/>
     <border>
       <left style="thin">
@@ -257,11 +330,22 @@
         <color rgb="FF000000"/>
       </bottom>
     </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="23">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -282,16 +366,37 @@
     <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="2" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -650,8 +755,40 @@
       <c r="Y4" s="5"/>
       <c r="Z4" s="5"/>
     </row>
-    <row r="5" ht="14.25" customHeight="1"/>
-    <row r="6" ht="14.25" customHeight="1"/>
+    <row r="5" ht="14.25" customHeight="1">
+      <c r="A5" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" ht="14.25" customHeight="1">
+      <c r="A6" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>24</v>
+      </c>
+    </row>
     <row r="7" ht="14.25" customHeight="1"/>
     <row r="8" ht="14.25" customHeight="1"/>
     <row r="9" ht="14.25" customHeight="1"/>
@@ -1647,17 +1784,20 @@
     <row r="999" ht="14.25" customHeight="1"/>
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="$A$1:$E$4"/>
+  <autoFilter ref="$A$1:$E$6"/>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="E2"/>
     <hyperlink r:id="rId2" ref="E3"/>
     <hyperlink r:id="rId3" ref="C4"/>
     <hyperlink r:id="rId4" ref="E4"/>
+    <hyperlink r:id="rId5" ref="C5"/>
+    <hyperlink r:id="rId6" ref="E5"/>
+    <hyperlink r:id="rId7" ref="E6"/>
   </hyperlinks>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="portrait"/>
-  <drawing r:id="rId5"/>
+  <drawing r:id="rId8"/>
 </worksheet>
 </file>
 
@@ -1675,102 +1815,102 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
-      <c r="A1" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>18</v>
+      <c r="A1" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>21</v>
+      <c r="A2" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>24</v>
+      <c r="A3" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>27</v>
+      <c r="A4" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>30</v>
+      <c r="A5" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>33</v>
+      <c r="A6" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>36</v>
+      <c r="A7" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>39</v>
+        <v>46</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>42</v>
+        <v>49</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1"/>
